--- a/report_2405.xlsx
+++ b/report_2405.xlsx
@@ -8682,9 +8682,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="B23" s="96" t="n">
-        <v>3.09</v>
+        <v>3.38</v>
       </c>
       <c r="C23" s="96" t="n">
         <v>3.09</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="B24" s="96" t="n">
-        <v>15.08</v>
+        <v>15.09</v>
       </c>
       <c r="C24" s="96" t="n">
         <v>15.08</v>
@@ -9028,13 +9028,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="97" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B25" s="96" t="n">
-        <v>8.93</v>
+        <v>62.36</v>
       </c>
       <c r="C25" s="96" t="n">
         <v>8.93</v>
@@ -9125,13 +9125,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="97" t="inlineStr">
+      <c r="A26" s="78" t="inlineStr">
         <is>
           <t>us500:RSI2</t>
         </is>
       </c>
       <c r="B26" s="96" t="n">
-        <v>8.93</v>
+        <v>62.36</v>
       </c>
       <c r="C26" s="96" t="n">
         <v>8.93</v>
@@ -9227,9 +9227,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B27" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C27" s="93" t="inlineStr">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="B28" s="96" t="n">
-        <v>-1.23</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C28" s="96" t="n">
         <v>-1.23</v>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="B29" s="96" t="n">
-        <v>5.71</v>
+        <v>7.11</v>
       </c>
       <c r="C29" s="96" t="n">
         <v>5.71</v>
@@ -9573,13 +9573,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="97" t="inlineStr">
+      <c r="A30" s="78" t="inlineStr">
         <is>
           <t>us30:RSI3</t>
         </is>
       </c>
       <c r="B30" s="96" t="n">
-        <v>2.58</v>
+        <v>50.71</v>
       </c>
       <c r="C30" s="96" t="n">
         <v>2.58</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="B31" s="96" t="n">
-        <v>10.72</v>
+        <v>42.3</v>
       </c>
       <c r="C31" s="96" t="n">
         <v>10.72</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B33" s="96" t="n">
-        <v>5</v>
+        <v>4.39</v>
       </c>
       <c r="C33" s="96" t="n">
         <v>5</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B34" s="96" t="n">
-        <v>18.31</v>
+        <v>16.7</v>
       </c>
       <c r="C34" s="96" t="n">
         <v>18.31</v>
@@ -10124,7 +10124,7 @@
         </is>
       </c>
       <c r="B35" s="96" t="n">
-        <v>17.23</v>
+        <v>16.98</v>
       </c>
       <c r="C35" s="96" t="n">
         <v>17.23</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="B36" s="96" t="n">
-        <v>17.23</v>
+        <v>16.98</v>
       </c>
       <c r="C36" s="96" t="n">
         <v>17.23</v>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="B53" s="96" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="C53" s="96" t="n">
         <v>0.28</v>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="B54" s="96" t="n">
-        <v>7.48</v>
+        <v>7.6</v>
       </c>
       <c r="C54" s="96" t="n">
         <v>7.3</v>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="B55" s="96" t="n">
-        <v>34.64</v>
+        <v>38.72</v>
       </c>
       <c r="C55" s="96" t="n">
         <v>31.52</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="B56" s="96" t="n">
-        <v>32.61</v>
+        <v>35.14</v>
       </c>
       <c r="C56" s="96" t="n">
         <v>30.77</v>
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B58" s="96" t="n">
-        <v>4.56</v>
+        <v>4.43</v>
       </c>
       <c r="C58" s="96" t="n">
         <v>4.41</v>
@@ -12752,7 +12752,7 @@
         </is>
       </c>
       <c r="B59" s="96" t="n">
-        <v>11.29</v>
+        <v>11.15</v>
       </c>
       <c r="C59" s="96" t="n">
         <v>11.05</v>
@@ -12849,7 +12849,7 @@
         </is>
       </c>
       <c r="B60" s="96" t="n">
-        <v>28.89</v>
+        <v>24.66</v>
       </c>
       <c r="C60" s="96" t="n">
         <v>26.09</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B61" s="96" t="n">
-        <v>36.1</v>
+        <v>33.42</v>
       </c>
       <c r="C61" s="96" t="n">
         <v>34.59</v>
@@ -13039,7 +13039,7 @@
     <row r="63">
       <c r="A63" s="92" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RSI6:23.96&lt;=30;us500:RSI2:8.93&lt;=28;us500:RSI2:8.93&lt;=22;us30:RSI3:2.58&lt;=25;ixic:RSI2:17.23&lt;=36;ixic:RSI2:17.23&lt;=35</t>
+          <t>今日买报：hk50:RSI6:23.96&lt;=30;ixic:RSI2:16.98&lt;=36;ixic:RSI2:16.98&lt;=35</t>
         </is>
       </c>
     </row>

--- a/report_2405.xlsx
+++ b/report_2405.xlsx
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B26" s="90" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="C26" s="90" t="n">
         <v>-0.3</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="B27" s="90" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="C27" s="90" t="n">
         <v>0.1</v>
